--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103711558</v>
       </c>
       <c r="B2" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596857.4482379535</v>
+        <v>596857</v>
       </c>
       <c r="R2" t="n">
-        <v>7072565.121316195</v>
+        <v>7072566</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>103711562</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596857.4482379535</v>
+        <v>596857</v>
       </c>
       <c r="R3" t="n">
-        <v>7072565.121316195</v>
+        <v>7072566</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -867,19 +847,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,51 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103711558</v>
+        <v>135273128</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596857</v>
+        <v>596934</v>
       </c>
       <c r="R2" t="n">
-        <v>7072566</v>
+        <v>7072445</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,70 +764,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103711562</v>
+        <v>135274102</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596857</v>
+        <v>596896</v>
       </c>
       <c r="R3" t="n">
-        <v>7072566</v>
+        <v>7072475</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -844,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,22 +871,661 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135274390</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596870</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7072510</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103711558</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596857</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7072566</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Maria Johansson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Maria Johansson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103711562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596857</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7072566</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135273373</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596934</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072445</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135273735</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596934</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7072445</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135274294</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596870</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7072510</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,6 +1527,228 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135270693</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596837</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7072309</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135274421</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596870</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7072510</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273128</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274102</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103711558</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103711562</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273373</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273735</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274294</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135270693</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1748,8 +1798,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135273128</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135274102</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135274390</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>135273373</v>
       </c>
       <c r="B7" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135273735</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>135274294</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135270693</v>
       </c>
       <c r="B10" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135274421</v>
       </c>
       <c r="B11" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135273128</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135274102</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135274390</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>135273373</v>
       </c>
       <c r="B7" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>135270693</v>
       </c>
       <c r="B10" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>135274421</v>
       </c>
       <c r="B11" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 61511-2025 artfynd.xlsx
+++ b/artfynd/A 61511-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103711558</v>
+        <v>135273128</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596857</v>
+        <v>596934</v>
       </c>
       <c r="R2" t="n">
-        <v>7072566</v>
+        <v>7072445</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,75 +769,71 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103711558</t>
+          <t>https://artportalen.se/Sighting/135273128</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103711562</v>
+        <v>135274102</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>79441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kullberg, Ång</t>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596857</v>
+        <v>596896</v>
       </c>
       <c r="R3" t="n">
-        <v>7072566</v>
+        <v>7072475</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-21</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,25 +881,926 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Johansson</t>
+          <t>Johanna Liljegren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135274102</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135274390</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596870</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7072510</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274390</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>103711558</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596857</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7072566</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103711558</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103711562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kullberg, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596857</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7072566</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/103711562</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135273373</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596934</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072445</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273373</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135273735</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596934</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7072445</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135273735</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135274294</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596870</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7072510</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274294</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135270693</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596837</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7072309</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135270693</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135274421</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596870</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7072510</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274421</t>
         </is>
       </c>
     </row>
@@ -894,6 +1808,14 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
